--- a/tools/excel/anssi/nis2/mapping-recyf-and-iso27001-2022.xlsx
+++ b/tools/excel/anssi/nis2/mapping-recyf-and-iso27001-2022.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ericlaubacher/Documents/GitHub/ciso-assistant-community/tools/excel/anssi/nis2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A688ED15-E63B-4546-8DD3-2321658AC14B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B4767A-D590-7E47-93E6-B3F3B1C329D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2509" uniqueCount="1289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2509" uniqueCount="1290">
   <si>
     <t>type</t>
   </si>
@@ -3986,6 +3986,9 @@
   </si>
   <si>
     <t>This control ensures that systems and data are safeguarded during audits by preventing unauthorized access, data leakage, or disruptions. Measures include using non-production environments, access restrictions, and confidentiality agreements to maintain system security and integrity.</t>
+  </si>
+  <si>
+    <t>ANSSI</t>
   </si>
 </sst>
 </file>
@@ -4393,7 +4396,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -4401,7 +4404,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
